--- a/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/02_LPASK3 - Eğitim ve Operatör Yeterliliği/EKG-IK-PLN-01_esneklik_cizelgesi_ve_haftalik_rotasyon_plani.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/02_LPASK3 - Eğitim ve Operatör Yeterliliği/EKG-IK-PLN-01_esneklik_cizelgesi_ve_haftalik_rotasyon_plani.xlsx
@@ -801,7 +801,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-IK-PLN-01&amp;C&amp;"Arial,Regular"&amp;11Esneklik Çizelgesi ve Haftalık Rotasyon Planı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 08.09.2026
+Revizyon nedeni: Çelişkili puanlar kaldırıldı; operasyon bazlı yetkili asıl/yedek ve tarihli rotasyon planı kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -967,7 +968,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-IK-PLN-01&amp;C&amp;"Arial,Regular"&amp;11Esneklik Çizelgesi ve Haftalık Rotasyon Planı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 08.09.2026
+Revizyon nedeni: Çelişkili puanlar kaldırıldı; operasyon bazlı yetkili asıl/yedek ve tarihli rotasyon planı kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>